--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ69"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128835471</v>
+        <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87144</v>
+        <v>87386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1985</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,16 +821,18 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo,Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700792</v>
+        <v>701070</v>
       </c>
       <c r="R3" t="n">
-        <v>6388508</v>
+        <v>6388490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,33 +883,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835471</t>
+          <t>https://artportalen.se/Sighting/137199971</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128835472</v>
+        <v>137195443</v>
       </c>
       <c r="B4" t="n">
-        <v>87144</v>
+        <v>87561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +922,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1985</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörkfjällig olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius melanotus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700957</v>
+        <v>700921</v>
       </c>
       <c r="R4" t="n">
-        <v>6388630</v>
+        <v>6388581</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +976,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,24 +1006,28 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835472</t>
+          <t>https://artportalen.se/Sighting/137195443</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128835473</v>
+        <v>128835471</v>
       </c>
       <c r="B5" t="n">
         <v>87144</v>
@@ -1051,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700804</v>
+        <v>700792</v>
       </c>
       <c r="R5" t="n">
-        <v>6388505</v>
+        <v>6388508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1133,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835473</t>
+          <t>https://artportalen.se/Sighting/128835471</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128835474</v>
+        <v>128835472</v>
       </c>
       <c r="B6" t="n">
         <v>87144</v>
@@ -1157,19 +1168,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700966</v>
+        <v>700957</v>
       </c>
       <c r="R6" t="n">
-        <v>6388635</v>
+        <v>6388630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1228,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,13 +1245,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835474</t>
+          <t>https://artportalen.se/Sighting/128835472</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128835475</v>
+        <v>128835473</v>
       </c>
       <c r="B7" t="n">
         <v>87144</v>
@@ -1282,7 +1289,7 @@
         <v>700804</v>
       </c>
       <c r="R7" t="n">
-        <v>6388482</v>
+        <v>6388505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,51 +1357,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835475</t>
+          <t>https://artportalen.se/Sighting/128835473</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128835462</v>
+        <v>128835474</v>
       </c>
       <c r="B8" t="n">
-        <v>87322</v>
+        <v>87144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700813</v>
+        <v>700966</v>
       </c>
       <c r="R8" t="n">
-        <v>6388546</v>
+        <v>6388635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,6 +1455,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1462,38 +1473,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835462</t>
+          <t>https://artportalen.se/Sighting/128835474</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128835463</v>
+        <v>128835475</v>
       </c>
       <c r="B9" t="n">
-        <v>87322</v>
+        <v>87144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Mörkfjällig olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius melanotus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700887</v>
+        <v>700804</v>
       </c>
       <c r="R9" t="n">
-        <v>6388581</v>
+        <v>6388482</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,13 +1585,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835463</t>
+          <t>https://artportalen.se/Sighting/128835475</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128835464</v>
+        <v>128835462</v>
       </c>
       <c r="B10" t="n">
         <v>87322</v>
@@ -1615,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700940</v>
+        <v>700813</v>
       </c>
       <c r="R10" t="n">
-        <v>6388612</v>
+        <v>6388546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,38 +1697,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835464</t>
+          <t>https://artportalen.se/Sighting/128835462</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128835469</v>
+        <v>128835463</v>
       </c>
       <c r="B11" t="n">
-        <v>87333</v>
+        <v>87322</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3599</v>
+        <v>1988</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,7 +1738,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700915</v>
+        <v>700887</v>
       </c>
       <c r="R11" t="n">
         <v>6388581</v>
@@ -1762,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,12 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 fk</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,38 +1809,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835469</t>
+          <t>https://artportalen.se/Sighting/128835463</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128835470</v>
+        <v>128835464</v>
       </c>
       <c r="B12" t="n">
-        <v>87333</v>
+        <v>87322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3599</v>
+        <v>1988</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700910</v>
+        <v>700940</v>
       </c>
       <c r="R12" t="n">
-        <v>6388586</v>
+        <v>6388612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,54 +1921,57 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835470</t>
+          <t>https://artportalen.se/Sighting/128835464</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128833066</v>
+        <v>137199979</v>
       </c>
       <c r="B13" t="n">
-        <v>87309</v>
+        <v>87515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>1988</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingbo,Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>701012</v>
+        <v>700852</v>
       </c>
       <c r="R13" t="n">
-        <v>6388573</v>
+        <v>6388406</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1986,12 +1995,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,55 +2019,60 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Bo karlstens, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833066</t>
+          <t>https://artportalen.se/Sighting/137199979</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128833067</v>
+        <v>137195424</v>
       </c>
       <c r="B14" t="n">
-        <v>87309</v>
+        <v>93292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>2057</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sandkremla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Russula torulosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,13 +2082,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700982</v>
+        <v>701130</v>
       </c>
       <c r="R14" t="n">
-        <v>6388557</v>
+        <v>6388529</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,12 +2112,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,49 +2142,53 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833067</t>
+          <t>https://artportalen.se/Sighting/137195424</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128833068</v>
+        <v>137195435</v>
       </c>
       <c r="B15" t="n">
-        <v>87309</v>
+        <v>93292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>2057</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sandkremla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Russula torulosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2160,13 +2198,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700938</v>
+        <v>700950</v>
       </c>
       <c r="R15" t="n">
-        <v>6388454</v>
+        <v>6388610</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,12 +2228,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,49 +2258,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833068</t>
+          <t>https://artportalen.se/Sighting/137195435</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128833069</v>
+        <v>137195437</v>
       </c>
       <c r="B16" t="n">
-        <v>87309</v>
+        <v>93292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>2057</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Sandkremla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Russula torulosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700967</v>
+        <v>700840</v>
       </c>
       <c r="R16" t="n">
-        <v>6388445</v>
+        <v>6388580</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,12 +2344,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,62 +2374,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833069</t>
+          <t>https://artportalen.se/Sighting/137195437</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128833070</v>
+        <v>128835469</v>
       </c>
       <c r="B17" t="n">
-        <v>87309</v>
+        <v>87333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>701026</v>
+        <v>700915</v>
       </c>
       <c r="R17" t="n">
-        <v>6388477</v>
+        <v>6388581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,9 +2463,24 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 fk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,62 +2495,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833070</t>
+          <t>https://artportalen.se/Sighting/128835469</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128833071</v>
+        <v>128835470</v>
       </c>
       <c r="B18" t="n">
-        <v>87309</v>
+        <v>87333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>701130</v>
+        <v>700910</v>
       </c>
       <c r="R18" t="n">
-        <v>6388509</v>
+        <v>6388586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,9 +2580,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,24 +2607,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833071</t>
+          <t>https://artportalen.se/Sighting/128835470</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128835493</v>
+        <v>128833066</v>
       </c>
       <c r="B19" t="n">
         <v>87309</v>
@@ -2564,14 +2655,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700828</v>
+        <v>701012</v>
       </c>
       <c r="R19" t="n">
-        <v>6388554</v>
+        <v>6388573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,19 +2692,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,24 +2709,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835493</t>
+          <t>https://artportalen.se/Sighting/128833066</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128835494</v>
+        <v>128833067</v>
       </c>
       <c r="B20" t="n">
         <v>87309</v>
@@ -2676,14 +2757,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700929</v>
+        <v>700982</v>
       </c>
       <c r="R20" t="n">
-        <v>6388692</v>
+        <v>6388557</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,19 +2794,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2740,24 +2811,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835494</t>
+          <t>https://artportalen.se/Sighting/128833067</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128835495</v>
+        <v>128833068</v>
       </c>
       <c r="B21" t="n">
         <v>87309</v>
@@ -2788,14 +2859,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700906</v>
+        <v>700938</v>
       </c>
       <c r="R21" t="n">
-        <v>6388731</v>
+        <v>6388454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,19 +2896,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2852,24 +2913,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835495</t>
+          <t>https://artportalen.se/Sighting/128833068</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128835497</v>
+        <v>128833069</v>
       </c>
       <c r="B22" t="n">
         <v>87309</v>
@@ -2900,14 +2961,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700948</v>
+        <v>700967</v>
       </c>
       <c r="R22" t="n">
-        <v>6388722</v>
+        <v>6388445</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,19 +2998,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,24 +3015,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835497</t>
+          <t>https://artportalen.se/Sighting/128833069</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128835498</v>
+        <v>128833070</v>
       </c>
       <c r="B23" t="n">
         <v>87309</v>
@@ -3012,14 +3063,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700817</v>
+        <v>701026</v>
       </c>
       <c r="R23" t="n">
-        <v>6388548</v>
+        <v>6388477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3049,19 +3100,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,24 +3117,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835498</t>
+          <t>https://artportalen.se/Sighting/128833070</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128835499</v>
+        <v>128833071</v>
       </c>
       <c r="B24" t="n">
         <v>87309</v>
@@ -3124,14 +3165,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700938</v>
+        <v>701130</v>
       </c>
       <c r="R24" t="n">
-        <v>6388610</v>
+        <v>6388509</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3161,19 +3202,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,62 +3219,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835499</t>
+          <t>https://artportalen.se/Sighting/128833071</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128833063</v>
+        <v>128835493</v>
       </c>
       <c r="B25" t="n">
-        <v>87170</v>
+        <v>87309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700953</v>
+        <v>700828</v>
       </c>
       <c r="R25" t="n">
-        <v>6388454</v>
+        <v>6388554</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,9 +3304,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,62 +3331,62 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833063</t>
+          <t>https://artportalen.se/Sighting/128835493</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128833064</v>
+        <v>128835494</v>
       </c>
       <c r="B26" t="n">
-        <v>87170</v>
+        <v>87309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>701018</v>
+        <v>700929</v>
       </c>
       <c r="R26" t="n">
-        <v>6388486</v>
+        <v>6388692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,9 +3416,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,62 +3443,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833064</t>
+          <t>https://artportalen.se/Sighting/128835494</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128833065</v>
+        <v>128835495</v>
       </c>
       <c r="B27" t="n">
-        <v>87170</v>
+        <v>87309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>701142</v>
+        <v>700906</v>
       </c>
       <c r="R27" t="n">
-        <v>6388527</v>
+        <v>6388731</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,9 +3528,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3494,27 +3555,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833065</t>
+          <t>https://artportalen.se/Sighting/128835495</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128835448</v>
+        <v>128835497</v>
       </c>
       <c r="B28" t="n">
-        <v>87146</v>
+        <v>87309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,21 +3583,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3546,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700817</v>
+        <v>700948</v>
       </c>
       <c r="R28" t="n">
-        <v>6388555</v>
+        <v>6388722</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3591,7 +3652,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,16 +3678,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835448</t>
+          <t>https://artportalen.se/Sighting/128835497</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128835449</v>
+        <v>128835498</v>
       </c>
       <c r="B29" t="n">
-        <v>87146</v>
+        <v>87309</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,21 +3695,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3658,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700916</v>
+        <v>700817</v>
       </c>
       <c r="R29" t="n">
-        <v>6388577</v>
+        <v>6388548</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3693,7 +3754,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3703,7 +3764,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,16 +3790,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835449</t>
+          <t>https://artportalen.se/Sighting/128835498</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128835450</v>
+        <v>128835499</v>
       </c>
       <c r="B30" t="n">
-        <v>87146</v>
+        <v>87309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,21 +3807,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3770,10 +3831,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700914</v>
+        <v>700938</v>
       </c>
       <c r="R30" t="n">
-        <v>6388586</v>
+        <v>6388610</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3866,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3876,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3841,54 +3902,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835450</t>
+          <t>https://artportalen.se/Sighting/128835499</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128835441</v>
+        <v>137195425</v>
       </c>
       <c r="B31" t="n">
-        <v>87391</v>
+        <v>87502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700883</v>
+        <v>701135</v>
       </c>
       <c r="R31" t="n">
-        <v>6388583</v>
+        <v>6388534</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3912,22 +3973,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,65 +4003,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835441</t>
+          <t>https://artportalen.se/Sighting/137195425</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128835442</v>
+        <v>137195426</v>
       </c>
       <c r="B32" t="n">
-        <v>87391</v>
+        <v>87502</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700952</v>
+        <v>701134</v>
       </c>
       <c r="R32" t="n">
-        <v>6388607</v>
+        <v>6388546</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4024,22 +4089,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,65 +4119,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835442</t>
+          <t>https://artportalen.se/Sighting/137195426</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128835443</v>
+        <v>137195432</v>
       </c>
       <c r="B33" t="n">
-        <v>87391</v>
+        <v>87502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700956</v>
+        <v>701015</v>
       </c>
       <c r="R33" t="n">
-        <v>6388619</v>
+        <v>6388582</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4136,22 +4205,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4166,65 +4235,71 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835443</t>
+          <t>https://artportalen.se/Sighting/137195432</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128835444</v>
+        <v>137199975</v>
       </c>
       <c r="B34" t="n">
-        <v>87391</v>
+        <v>87502</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo,Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700957</v>
+        <v>700855</v>
       </c>
       <c r="R34" t="n">
-        <v>6388621</v>
+        <v>6388391</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4248,22 +4323,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4272,71 +4347,73 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Bo karlstens, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835444</t>
+          <t>https://artportalen.se/Sighting/137199975</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128835454</v>
+        <v>128833063</v>
       </c>
       <c r="B35" t="n">
-        <v>91382</v>
+        <v>87170</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5735</v>
+        <v>3712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700887</v>
+        <v>700953</v>
       </c>
       <c r="R35" t="n">
-        <v>6388572</v>
+        <v>6388454</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,99 +4443,79 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835454</t>
+          <t>https://artportalen.se/Sighting/128833063</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128835455</v>
+        <v>128833064</v>
       </c>
       <c r="B36" t="n">
-        <v>91382</v>
+        <v>87170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5735</v>
+        <v>3712</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700897</v>
+        <v>701018</v>
       </c>
       <c r="R36" t="n">
-        <v>6388579</v>
+        <v>6388486</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4488,93 +4545,79 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835455</t>
+          <t>https://artportalen.se/Sighting/128833064</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128835461</v>
+        <v>128833065</v>
       </c>
       <c r="B37" t="n">
-        <v>91435</v>
+        <v>87170</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700816</v>
+        <v>701142</v>
       </c>
       <c r="R37" t="n">
-        <v>6388491</v>
+        <v>6388527</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,94 +4647,81 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835461</t>
+          <t>https://artportalen.se/Sighting/128833065</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135045765</v>
+        <v>137199976</v>
       </c>
       <c r="B38" t="n">
-        <v>43309</v>
+        <v>87363</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101260</v>
+        <v>3712</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo,Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700840</v>
+        <v>700855</v>
       </c>
       <c r="R38" t="n">
-        <v>6388251</v>
+        <v>6388391</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4718,12 +4748,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,75 +4772,76 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Bo karlstens, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045765</t>
+          <t>https://artportalen.se/Sighting/137199976</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135045766</v>
+        <v>128835448</v>
       </c>
       <c r="B39" t="n">
-        <v>43309</v>
+        <v>87146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101260</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700883</v>
+        <v>700817</v>
       </c>
       <c r="R39" t="n">
-        <v>6388209</v>
+        <v>6388555</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4824,12 +4865,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4844,65 +4895,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045766</t>
+          <t>https://artportalen.se/Sighting/128835448</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135046035</v>
+        <v>128835449</v>
       </c>
       <c r="B40" t="n">
-        <v>45055</v>
+        <v>87146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102018</v>
+        <v>3762</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700847</v>
+        <v>700916</v>
       </c>
       <c r="R40" t="n">
-        <v>6388244</v>
+        <v>6388577</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4926,12 +4977,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,65 +5007,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046035</t>
+          <t>https://artportalen.se/Sighting/128835449</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135046042</v>
+        <v>128835450</v>
       </c>
       <c r="B41" t="n">
-        <v>45055</v>
+        <v>87146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102018</v>
+        <v>3762</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700899</v>
+        <v>700914</v>
       </c>
       <c r="R41" t="n">
-        <v>6388196</v>
+        <v>6388586</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5028,12 +5089,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5042,72 +5113,71 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046042</t>
+          <t>https://artportalen.se/Sighting/128835450</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135045810</v>
+        <v>137195429</v>
       </c>
       <c r="B42" t="n">
-        <v>40525</v>
+        <v>87339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102406</v>
+        <v>3762</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Solvändesäckmal</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Coleophora ochrea</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Haworth, 1828)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700841</v>
+        <v>701026</v>
       </c>
       <c r="R42" t="n">
-        <v>6388248</v>
+        <v>6388600</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5131,12 +5201,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5151,62 +5231,66 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045810</t>
+          <t>https://artportalen.se/Sighting/137195429</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128833059</v>
+        <v>128835441</v>
       </c>
       <c r="B43" t="n">
-        <v>8455</v>
+        <v>87391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>3767</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700942</v>
+        <v>700883</v>
       </c>
       <c r="R43" t="n">
-        <v>6388538</v>
+        <v>6388583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5236,9 +5320,19 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5253,65 +5347,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833059</t>
+          <t>https://artportalen.se/Sighting/128835441</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135045850</v>
+        <v>128835442</v>
       </c>
       <c r="B44" t="n">
-        <v>43229</v>
+        <v>87391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>201028</v>
+        <v>3767</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700859</v>
+        <v>700952</v>
       </c>
       <c r="R44" t="n">
-        <v>6388234</v>
+        <v>6388607</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5335,12 +5429,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5355,27 +5459,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045850</t>
+          <t>https://artportalen.se/Sighting/128835442</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135045821</v>
+        <v>128835443</v>
       </c>
       <c r="B45" t="n">
-        <v>45053</v>
+        <v>87391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5383,37 +5487,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>201164</v>
+        <v>3767</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700847</v>
+        <v>700956</v>
       </c>
       <c r="R45" t="n">
-        <v>6388244</v>
+        <v>6388619</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5437,12 +5541,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5457,69 +5571,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045821</t>
+          <t>https://artportalen.se/Sighting/128835443</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135046025</v>
+        <v>128835444</v>
       </c>
       <c r="B46" t="n">
-        <v>43991</v>
+        <v>87391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>215320</v>
+        <v>3767</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brokigt timjansmott</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pempeliella ornatella</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700899</v>
+        <v>700957</v>
       </c>
       <c r="R46" t="n">
-        <v>6388196</v>
+        <v>6388621</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5543,12 +5653,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5563,65 +5683,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046025</t>
+          <t>https://artportalen.se/Sighting/128835444</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135045846</v>
+        <v>137195434</v>
       </c>
       <c r="B47" t="n">
-        <v>111342</v>
+        <v>87584</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219677</v>
+        <v>3767</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700881</v>
+        <v>700951</v>
       </c>
       <c r="R47" t="n">
-        <v>6388215</v>
+        <v>6388608</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5645,12 +5765,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Större mycel, 9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5665,62 +5800,66 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045846</t>
+          <t>https://artportalen.se/Sighting/137195434</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135045938</v>
+        <v>137195440</v>
       </c>
       <c r="B48" t="n">
-        <v>108279</v>
+        <v>87584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>3767</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700859</v>
+        <v>700828</v>
       </c>
       <c r="R48" t="n">
-        <v>6388234</v>
+        <v>6388555</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5747,12 +5886,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5767,65 +5916,69 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045938</t>
+          <t>https://artportalen.se/Sighting/137195440</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135045818</v>
+        <v>137195442</v>
       </c>
       <c r="B49" t="n">
-        <v>109979</v>
+        <v>87584</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220204</v>
+        <v>3767</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700847</v>
+        <v>700809</v>
       </c>
       <c r="R49" t="n">
-        <v>6388244</v>
+        <v>6388558</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5849,12 +6002,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5869,65 +6032,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045818</t>
+          <t>https://artportalen.se/Sighting/137195442</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135045819</v>
+        <v>137195445</v>
       </c>
       <c r="B50" t="n">
-        <v>109979</v>
+        <v>87584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220204</v>
+        <v>3767</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700856</v>
+        <v>700937</v>
       </c>
       <c r="R50" t="n">
-        <v>6388239</v>
+        <v>6388580</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5951,12 +6118,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5971,65 +6148,72 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045819</t>
+          <t>https://artportalen.se/Sighting/137195445</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135045757</v>
+        <v>128835454</v>
       </c>
       <c r="B51" t="n">
-        <v>110242</v>
+        <v>91382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220299</v>
+        <v>5735</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700859</v>
+        <v>700887</v>
       </c>
       <c r="R51" t="n">
-        <v>6388234</v>
+        <v>6388572</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6053,12 +6237,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, Minst 47 fk i en 13 Linje!! Undr En 7-8 meter hög en</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6067,33 +6266,38 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045757</t>
+          <t>https://artportalen.se/Sighting/128835454</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128835492</v>
+        <v>128835455</v>
       </c>
       <c r="B52" t="n">
-        <v>106812</v>
+        <v>91382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6101,21 +6305,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220785</v>
+        <v>5735</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6125,10 +6329,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700799</v>
+        <v>700897</v>
       </c>
       <c r="R52" t="n">
-        <v>6388520</v>
+        <v>6388579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6160,7 +6364,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6170,12 +6374,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6184,6 +6383,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6201,54 +6401,57 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835492</t>
+          <t>https://artportalen.se/Sighting/128835455</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135046113</v>
+        <v>128835461</v>
       </c>
       <c r="B53" t="n">
-        <v>107680</v>
+        <v>91435</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221849</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700809</v>
+        <v>700816</v>
       </c>
       <c r="R53" t="n">
-        <v>6388274</v>
+        <v>6388491</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6272,12 +6475,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6286,33 +6499,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046113</t>
+          <t>https://artportalen.se/Sighting/128835461</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135046114</v>
+        <v>137199974</v>
       </c>
       <c r="B54" t="n">
-        <v>107680</v>
+        <v>93462</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6320,34 +6534,36 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Follingbo,Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700876</v>
+        <v>700856</v>
       </c>
       <c r="R54" t="n">
-        <v>6388218</v>
+        <v>6388393</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6374,12 +6590,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6388,68 +6614,77 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046114</t>
+          <t>https://artportalen.se/Sighting/137199974</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135046115</v>
+        <v>135045765</v>
       </c>
       <c r="B55" t="n">
-        <v>107680</v>
+        <v>43309</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>101260</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700907</v>
+        <v>700840</v>
       </c>
       <c r="R55" t="n">
-        <v>6388189</v>
+        <v>6388251</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6507,47 +6742,55 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046115</t>
+          <t>https://artportalen.se/Sighting/135045765</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135045855</v>
+        <v>135045766</v>
       </c>
       <c r="B56" t="n">
-        <v>104801</v>
+        <v>43309</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>224416</v>
+        <v>101260</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Phengaris arion</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700809</v>
+        <v>700883</v>
       </c>
       <c r="R56" t="n">
-        <v>6388274</v>
+        <v>6388209</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6605,36 +6848,40 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045855</t>
+          <t>https://artportalen.se/Sighting/135045766</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135045887</v>
+        <v>135046035</v>
       </c>
       <c r="B57" t="n">
-        <v>104801</v>
+        <v>45055</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224416</v>
+        <v>102018</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6703,36 +6950,40 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045887</t>
+          <t>https://artportalen.se/Sighting/135046035</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135045888</v>
+        <v>135046042</v>
       </c>
       <c r="B58" t="n">
-        <v>104801</v>
+        <v>45055</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>224416</v>
+        <v>102018</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6740,10 +6991,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700856</v>
+        <v>700899</v>
       </c>
       <c r="R58" t="n">
-        <v>6388239</v>
+        <v>6388196</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6784,6 +7035,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6801,16 +7053,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045888</t>
+          <t>https://artportalen.se/Sighting/135046042</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>105104386</v>
+        <v>135045810</v>
       </c>
       <c r="B59" t="n">
-        <v>106650</v>
+        <v>40525</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,33 +7070,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>225197</v>
+        <v>102406</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Äkta ljungsnärja</t>
+          <t>Solvändesäckmal</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Coleophora ochrea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Haworth, 1828)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Follingbomasten 300 m V, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>701144</v>
+        <v>700841</v>
       </c>
       <c r="R59" t="n">
-        <v>6388381</v>
+        <v>6388248</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6868,17 +7124,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>1996-12-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rosendal 1:17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6889,75 +7140,66 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Alvarlik kalkhällmark, parasit på Gulmåra, Ögontröst, Praktbrunört</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105104386</t>
+          <t>https://artportalen.se/Sighting/135045810</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128835480</v>
+        <v>128833059</v>
       </c>
       <c r="B60" t="n">
-        <v>92688</v>
+        <v>8455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>232138</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700814</v>
+        <v>700942</v>
       </c>
       <c r="R60" t="n">
-        <v>6388491</v>
+        <v>6388538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,19 +7229,9 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>16:59</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>16:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7014,65 +7246,65 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835480</t>
+          <t>https://artportalen.se/Sighting/128833059</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128833061</v>
+        <v>135045850</v>
       </c>
       <c r="B61" t="n">
-        <v>87262</v>
+        <v>43229</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248956</v>
+        <v>201028</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700935</v>
+        <v>700859</v>
       </c>
       <c r="R61" t="n">
-        <v>6388458</v>
+        <v>6388234</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7096,12 +7328,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7116,65 +7348,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833061</t>
+          <t>https://artportalen.se/Sighting/135045850</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128833052</v>
+        <v>135045821</v>
       </c>
       <c r="B62" t="n">
-        <v>87346</v>
+        <v>45053</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6003295</v>
+        <v>201164</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>701151</v>
+        <v>700847</v>
       </c>
       <c r="R62" t="n">
-        <v>6388524</v>
+        <v>6388244</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7198,12 +7430,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7212,34 +7444,33 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833052</t>
+          <t>https://artportalen.se/Sighting/135045821</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128833053</v>
+        <v>135046025</v>
       </c>
       <c r="B63" t="n">
-        <v>87346</v>
+        <v>43991</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7247,37 +7478,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6003295</v>
+        <v>215320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Brokigt timjansmott</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Pempeliella ornatella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700979</v>
+        <v>700899</v>
       </c>
       <c r="R63" t="n">
-        <v>6388550</v>
+        <v>6388196</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7301,12 +7536,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7315,72 +7550,71 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833053</t>
+          <t>https://artportalen.se/Sighting/135046025</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128833054</v>
+        <v>135045846</v>
       </c>
       <c r="B64" t="n">
-        <v>87346</v>
+        <v>111342</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>219677</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700966</v>
+        <v>700881</v>
       </c>
       <c r="R64" t="n">
-        <v>6388444</v>
+        <v>6388215</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7404,12 +7638,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7418,34 +7652,33 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833054</t>
+          <t>https://artportalen.se/Sighting/135045846</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128833055</v>
+        <v>135045938</v>
       </c>
       <c r="B65" t="n">
-        <v>87346</v>
+        <v>108279</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7453,37 +7686,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>220079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700996</v>
+        <v>700859</v>
       </c>
       <c r="R65" t="n">
-        <v>6388473</v>
+        <v>6388234</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7507,12 +7740,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7521,34 +7754,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833055</t>
+          <t>https://artportalen.se/Sighting/135045938</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128833056</v>
+        <v>135045818</v>
       </c>
       <c r="B66" t="n">
-        <v>87346</v>
+        <v>109979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7556,37 +7788,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>220204</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>701017</v>
+        <v>700847</v>
       </c>
       <c r="R66" t="n">
-        <v>6388485</v>
+        <v>6388244</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7610,12 +7842,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,34 +7856,33 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833056</t>
+          <t>https://artportalen.se/Sighting/135045818</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128833057</v>
+        <v>135045819</v>
       </c>
       <c r="B67" t="n">
-        <v>87346</v>
+        <v>109979</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7659,37 +7890,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>220204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>701053</v>
+        <v>700856</v>
       </c>
       <c r="R67" t="n">
-        <v>6388488</v>
+        <v>6388239</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7713,12 +7944,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7727,34 +7958,33 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833057</t>
+          <t>https://artportalen.se/Sighting/135045819</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128835465</v>
+        <v>135045757</v>
       </c>
       <c r="B68" t="n">
-        <v>87346</v>
+        <v>110242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7762,37 +7992,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6003295</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700869</v>
+        <v>700859</v>
       </c>
       <c r="R68" t="n">
-        <v>6388563</v>
+        <v>6388234</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7816,22 +8046,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7840,56 +8060,55 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835465</t>
+          <t>https://artportalen.se/Sighting/135045757</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128835466</v>
+        <v>128835492</v>
       </c>
       <c r="B69" t="n">
-        <v>87346</v>
+        <v>106812</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7899,10 +8118,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700824</v>
+        <v>700799</v>
       </c>
       <c r="R69" t="n">
-        <v>6388554</v>
+        <v>6388520</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7934,7 +8153,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7944,7 +8163,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7953,7 +8177,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7971,7 +8194,2944 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128835492</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135046113</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107680</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>700809</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6388274</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046113</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135046114</v>
+      </c>
+      <c r="B71" t="n">
+        <v>107680</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>700876</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6388218</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046114</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135046115</v>
+      </c>
+      <c r="B72" t="n">
+        <v>107680</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>700907</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6388189</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046115</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135045855</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104801</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>700809</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6388274</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045855</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135045887</v>
+      </c>
+      <c r="B74" t="n">
+        <v>104801</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>700847</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6388244</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045887</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135045888</v>
+      </c>
+      <c r="B75" t="n">
+        <v>104801</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>700856</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6388239</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135045888</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105104386</v>
+      </c>
+      <c r="B76" t="n">
+        <v>106650</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>225197</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Äkta ljungsnärja</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Follingbomasten 300 m V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>701144</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6388381</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rosendal 1:17</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Alvarlik kalkhällmark, parasit på Gulmåra, Ögontröst, Praktbrunört</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105104386</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128835480</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>700814</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6388491</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835480</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128833061</v>
+      </c>
+      <c r="B78" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>700935</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6388458</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833061</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137195444</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>700928</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6388587</v>
+      </c>
+      <c r="S79" t="n">
+        <v>22</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195444</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128833052</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>701151</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6388524</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833052</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128833053</v>
+      </c>
+      <c r="B81" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>700979</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6388550</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833053</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128833054</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>700966</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6388444</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833054</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128833055</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>700996</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6388473</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833055</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128833056</v>
+      </c>
+      <c r="B84" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>701017</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6388485</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833056</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128833057</v>
+      </c>
+      <c r="B85" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>701053</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6388488</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833057</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128835465</v>
+      </c>
+      <c r="B86" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>700869</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6388563</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835465</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128835466</v>
+      </c>
+      <c r="B87" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>700824</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6388554</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128835466</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>137195422</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>701158</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6388516</v>
+      </c>
+      <c r="S88" t="n">
+        <v>6</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195422</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>137195427</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>701052</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6388594</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195427</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>137195428</v>
+      </c>
+      <c r="B90" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>701024</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6388599</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195428</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>137195431</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>701026</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6388602</v>
+      </c>
+      <c r="S91" t="n">
+        <v>6</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195431</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>137195436</v>
+      </c>
+      <c r="B92" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>700870</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6388557</v>
+      </c>
+      <c r="S92" t="n">
+        <v>7</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195436</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>137195439</v>
+      </c>
+      <c r="B93" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>700852</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6388564</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195439</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>137195446</v>
+      </c>
+      <c r="B94" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>701022</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6388627</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195446</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>137199973</v>
+      </c>
+      <c r="B95" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Follingbo,Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>701051</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6388472</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137199973</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>137199977</v>
+      </c>
+      <c r="B96" t="n">
+        <v>87539</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Follingbo,Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>700856</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6388393</v>
+      </c>
+      <c r="S96" t="n">
+        <v>19</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137199977</t>
         </is>
       </c>
     </row>
@@ -8045,6 +11205,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87386</v>
+        <v>87388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137195443</v>
       </c>
       <c r="B4" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137199979</v>
       </c>
       <c r="B13" t="n">
-        <v>87515</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>137195424</v>
       </c>
       <c r="B14" t="n">
-        <v>93292</v>
+        <v>93294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137195435</v>
       </c>
       <c r="B15" t="n">
-        <v>93292</v>
+        <v>93294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>137195437</v>
       </c>
       <c r="B16" t="n">
-        <v>93292</v>
+        <v>93294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>137195425</v>
       </c>
       <c r="B31" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>137195426</v>
       </c>
       <c r="B32" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137195432</v>
       </c>
       <c r="B33" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>137199975</v>
       </c>
       <c r="B34" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>137199976</v>
       </c>
       <c r="B38" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>137195429</v>
       </c>
       <c r="B42" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>137195434</v>
       </c>
       <c r="B47" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>137195440</v>
       </c>
       <c r="B48" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137195442</v>
       </c>
       <c r="B49" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>137195445</v>
       </c>
       <c r="B50" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>137199974</v>
       </c>
       <c r="B54" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>137195444</v>
       </c>
       <c r="B79" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>137195422</v>
       </c>
       <c r="B88" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>137195427</v>
       </c>
       <c r="B89" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>137195428</v>
       </c>
       <c r="B90" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137195431</v>
       </c>
       <c r="B91" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>137195436</v>
       </c>
       <c r="B92" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>137195439</v>
       </c>
       <c r="B93" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>137195446</v>
       </c>
       <c r="B94" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>137199973</v>
       </c>
       <c r="B95" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>137199977</v>
       </c>
       <c r="B96" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93307</v>
+        <v>93309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93307</v>
+        <v>93309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93307</v>
+        <v>93309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87599</v>
+        <v>87601</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89355</v>
+        <v>89357</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137241110</v>
       </c>
       <c r="B72" t="n">
-        <v>58883</v>
+        <v>58885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>137195444</v>
       </c>
       <c r="B89" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137241119</v>
       </c>
       <c r="B90" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>137195422</v>
       </c>
       <c r="B99" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137195427</v>
       </c>
       <c r="B100" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137195428</v>
       </c>
       <c r="B101" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137195431</v>
       </c>
       <c r="B102" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>137195436</v>
       </c>
       <c r="B103" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>137195439</v>
       </c>
       <c r="B104" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>137195446</v>
       </c>
       <c r="B105" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137199973</v>
       </c>
       <c r="B106" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>137199977</v>
       </c>
       <c r="B107" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>137241106</v>
       </c>
       <c r="B108" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>137241111</v>
       </c>
       <c r="B109" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>137241112</v>
       </c>
       <c r="B110" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>137241126</v>
       </c>
       <c r="B111" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93309</v>
+        <v>93312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93309</v>
+        <v>93312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93309</v>
+        <v>93312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87601</v>
+        <v>87604</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89357</v>
+        <v>89360</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>137195444</v>
       </c>
       <c r="B89" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137241119</v>
       </c>
       <c r="B90" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>137195422</v>
       </c>
       <c r="B99" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137195427</v>
       </c>
       <c r="B100" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137195428</v>
       </c>
       <c r="B101" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137195431</v>
       </c>
       <c r="B102" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>137195436</v>
       </c>
       <c r="B103" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>137195439</v>
       </c>
       <c r="B104" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>137195446</v>
       </c>
       <c r="B105" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>137199973</v>
       </c>
       <c r="B106" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>137199977</v>
       </c>
       <c r="B107" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>137241106</v>
       </c>
       <c r="B108" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>137241111</v>
       </c>
       <c r="B109" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>137241112</v>
       </c>
       <c r="B110" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>137241126</v>
       </c>
       <c r="B111" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ111"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93312</v>
+        <v>93322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93312</v>
+        <v>93322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93312</v>
+        <v>93322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87625</v>
+        <v>87635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87604</v>
+        <v>87614</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89360</v>
+        <v>89370</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137241110</v>
       </c>
       <c r="B72" t="n">
-        <v>58885</v>
+        <v>58895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8838,45 +8838,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135045938</v>
+        <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>108279</v>
+        <v>111503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220079</v>
+        <v>219677</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700859</v>
+        <v>700906</v>
       </c>
       <c r="R75" t="n">
-        <v>6388234</v>
+        <v>6388207</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8903,12 +8903,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8928,57 +8928,57 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045938</t>
+          <t>https://artportalen.se/Sighting/137314147</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135045818</v>
+        <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>109979</v>
+        <v>108179</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220204</v>
+        <v>219933</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700847</v>
+        <v>700673</v>
       </c>
       <c r="R76" t="n">
-        <v>6388244</v>
+        <v>6388417</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9030,22 +9030,22 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045818</t>
+          <t>https://artportalen.se/Sighting/137314136</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135045819</v>
+        <v>135045938</v>
       </c>
       <c r="B77" t="n">
-        <v>109979</v>
+        <v>108279</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9053,21 +9053,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220204</v>
+        <v>220079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700856</v>
+        <v>700859</v>
       </c>
       <c r="R77" t="n">
-        <v>6388239</v>
+        <v>6388234</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9138,16 +9138,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045819</t>
+          <t>https://artportalen.se/Sighting/135045938</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135045757</v>
+        <v>135045818</v>
       </c>
       <c r="B78" t="n">
-        <v>110242</v>
+        <v>109979</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9155,16 +9155,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>220204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9179,10 +9179,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700859</v>
+        <v>700847</v>
       </c>
       <c r="R78" t="n">
-        <v>6388234</v>
+        <v>6388244</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9240,33 +9240,33 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045757</t>
+          <t>https://artportalen.se/Sighting/135045818</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128835492</v>
+        <v>135045819</v>
       </c>
       <c r="B79" t="n">
-        <v>106812</v>
+        <v>109979</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>220204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9277,17 +9277,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700799</v>
+        <v>700856</v>
       </c>
       <c r="R79" t="n">
-        <v>6388520</v>
+        <v>6388239</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9311,27 +9311,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Mycket hlgvuxen 12+ Meter</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9346,27 +9331,27 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835492</t>
+          <t>https://artportalen.se/Sighting/135045819</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135046113</v>
+        <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>107680</v>
+        <v>110134</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9374,16 +9359,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221849</v>
+        <v>220204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9394,14 +9379,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700809</v>
+        <v>700799</v>
       </c>
       <c r="R80" t="n">
-        <v>6388274</v>
+        <v>6388295</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9428,12 +9413,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9453,22 +9438,22 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046113</t>
+          <t>https://artportalen.se/Sighting/137314143</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135046114</v>
+        <v>135045757</v>
       </c>
       <c r="B81" t="n">
-        <v>107680</v>
+        <v>110242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9476,16 +9461,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9500,10 +9485,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700876</v>
+        <v>700859</v>
       </c>
       <c r="R81" t="n">
-        <v>6388218</v>
+        <v>6388234</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9561,16 +9546,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046114</t>
+          <t>https://artportalen.se/Sighting/135045757</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135046115</v>
+        <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>107680</v>
+        <v>110398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9578,16 +9563,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9598,14 +9583,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700907</v>
+        <v>700600</v>
       </c>
       <c r="R82" t="n">
-        <v>6388189</v>
+        <v>6388509</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9632,12 +9617,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9657,22 +9642,22 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046115</t>
+          <t>https://artportalen.se/Sighting/137314130</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135045855</v>
+        <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>104801</v>
+        <v>110398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9680,30 +9665,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700809</v>
+        <v>700640</v>
       </c>
       <c r="R83" t="n">
-        <v>6388274</v>
+        <v>6388452</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9730,12 +9719,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9755,22 +9744,22 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045855</t>
+          <t>https://artportalen.se/Sighting/137314134</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135045887</v>
+        <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>104801</v>
+        <v>110398</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9778,30 +9767,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700847</v>
+        <v>700747</v>
       </c>
       <c r="R84" t="n">
-        <v>6388244</v>
+        <v>6388337</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9828,12 +9821,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9853,22 +9846,22 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045887</t>
+          <t>https://artportalen.se/Sighting/137314140</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135045888</v>
+        <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>104801</v>
+        <v>110398</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9876,30 +9869,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>224416</v>
+        <v>220299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700856</v>
+        <v>700877</v>
       </c>
       <c r="R85" t="n">
-        <v>6388239</v>
+        <v>6388227</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9926,12 +9923,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9951,53 +9948,57 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Tobias Ivarsson</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135045888</t>
+          <t>https://artportalen.se/Sighting/137314146</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>105104386</v>
+        <v>128835492</v>
       </c>
       <c r="B86" t="n">
-        <v>106650</v>
+        <v>106812</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>225197</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Äkta ljungsnärja</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Follingbomasten 300 m V, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>701144</v>
+        <v>700799</v>
       </c>
       <c r="R86" t="n">
-        <v>6388381</v>
+        <v>6388520</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10024,17 +10025,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>1996-12-31</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Rosendal 1:17</t>
+          <t>Mycket hlgvuxen 12+ Meter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10045,78 +10056,69 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Alvarlik kalkhällmark, parasit på Gulmåra, Ögontröst, Praktbrunört</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105104386</t>
+          <t>https://artportalen.se/Sighting/128835492</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128835480</v>
+        <v>135046113</v>
       </c>
       <c r="B87" t="n">
-        <v>92688</v>
+        <v>107680</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>232138</v>
+        <v>221849</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700814</v>
+        <v>700809</v>
       </c>
       <c r="R87" t="n">
-        <v>6388491</v>
+        <v>6388274</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10140,22 +10142,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10170,65 +10162,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835480</t>
+          <t>https://artportalen.se/Sighting/135046113</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128833061</v>
+        <v>135046114</v>
       </c>
       <c r="B88" t="n">
-        <v>87262</v>
+        <v>107680</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700935</v>
+        <v>700876</v>
       </c>
       <c r="R88" t="n">
-        <v>6388458</v>
+        <v>6388218</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10252,12 +10244,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10272,65 +10264,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833061</t>
+          <t>https://artportalen.se/Sighting/135046114</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137195444</v>
+        <v>135046115</v>
       </c>
       <c r="B89" t="n">
-        <v>87475</v>
+        <v>107680</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700928</v>
+        <v>700907</v>
       </c>
       <c r="R89" t="n">
-        <v>6388587</v>
+        <v>6388189</v>
       </c>
       <c r="S89" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10354,22 +10346,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10384,69 +10366,65 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195444</t>
+          <t>https://artportalen.se/Sighting/135046115</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137241119</v>
+        <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>87475</v>
+        <v>107834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Follingbo, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700919</v>
+        <v>700626</v>
       </c>
       <c r="R90" t="n">
-        <v>6388559</v>
+        <v>6388471</v>
       </c>
       <c r="S90" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10470,22 +10448,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10494,38 +10462,33 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137241119</t>
+          <t>https://artportalen.se/Sighting/137314198</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128833052</v>
+        <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>87346</v>
+        <v>107834</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10533,37 +10496,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>701151</v>
+        <v>700662</v>
       </c>
       <c r="R91" t="n">
-        <v>6388524</v>
+        <v>6388423</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10587,12 +10550,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10601,34 +10564,33 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833052</t>
+          <t>https://artportalen.se/Sighting/137314199</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128833053</v>
+        <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>87346</v>
+        <v>107834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10636,37 +10598,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700979</v>
+        <v>700808</v>
       </c>
       <c r="R92" t="n">
-        <v>6388550</v>
+        <v>6388318</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10690,12 +10652,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10704,34 +10666,33 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833053</t>
+          <t>https://artportalen.se/Sighting/137314200</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128833054</v>
+        <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>87346</v>
+        <v>107834</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10739,37 +10700,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700966</v>
+        <v>700815</v>
       </c>
       <c r="R93" t="n">
-        <v>6388444</v>
+        <v>6388283</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10793,12 +10754,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10807,34 +10768,33 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833054</t>
+          <t>https://artportalen.se/Sighting/137314201</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128833055</v>
+        <v>135045855</v>
       </c>
       <c r="B94" t="n">
-        <v>87346</v>
+        <v>104801</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10842,37 +10802,33 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700996</v>
+        <v>700809</v>
       </c>
       <c r="R94" t="n">
-        <v>6388473</v>
+        <v>6388274</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10896,12 +10852,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10910,34 +10866,33 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833055</t>
+          <t>https://artportalen.se/Sighting/135045855</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128833056</v>
+        <v>135045887</v>
       </c>
       <c r="B95" t="n">
-        <v>87346</v>
+        <v>104801</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10945,37 +10900,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>701017</v>
+        <v>700847</v>
       </c>
       <c r="R95" t="n">
-        <v>6388485</v>
+        <v>6388244</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10999,12 +10950,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11013,34 +10964,33 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833056</t>
+          <t>https://artportalen.se/Sighting/135045887</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128833057</v>
+        <v>135045888</v>
       </c>
       <c r="B96" t="n">
-        <v>87346</v>
+        <v>104801</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11048,37 +10998,33 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Länsväg 143 mellan Visbytravet och Folingbo, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>701053</v>
+        <v>700856</v>
       </c>
       <c r="R96" t="n">
-        <v>6388488</v>
+        <v>6388239</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11102,12 +11048,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11116,34 +11062,33 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jan Henriksson, Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128833057</t>
+          <t>https://artportalen.se/Sighting/135045888</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128835465</v>
+        <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>87346</v>
+        <v>104949</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11151,37 +11096,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700869</v>
+        <v>700687</v>
       </c>
       <c r="R97" t="n">
-        <v>6388563</v>
+        <v>6388403</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11205,22 +11146,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11229,34 +11160,33 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835465</t>
+          <t>https://artportalen.se/Sighting/137314076</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128835466</v>
+        <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>87346</v>
+        <v>104949</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11264,37 +11194,33 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Follingsbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700824</v>
+        <v>700585</v>
       </c>
       <c r="R98" t="n">
-        <v>6388554</v>
+        <v>6388510</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11318,22 +11244,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11342,34 +11258,33 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jan Henriksson, Johan Henriksson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128835466</t>
+          <t>https://artportalen.se/Sighting/137314128</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137195422</v>
+        <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>87559</v>
+        <v>104949</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11377,37 +11292,33 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>701158</v>
+        <v>700601</v>
       </c>
       <c r="R99" t="n">
-        <v>6388516</v>
+        <v>6388497</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11431,22 +11342,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11461,31 +11362,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195422</t>
+          <t>https://artportalen.se/Sighting/137314131</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137195427</v>
+        <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>87559</v>
+        <v>104949</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11493,34 +11390,30 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>701052</v>
+        <v>700731</v>
       </c>
       <c r="R100" t="n">
-        <v>6388594</v>
+        <v>6388353</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11547,22 +11440,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11577,31 +11460,27 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195427</t>
+          <t>https://artportalen.se/Sighting/137314139</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137195428</v>
+        <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>87559</v>
+        <v>104949</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11609,37 +11488,33 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>701024</v>
+        <v>700761</v>
       </c>
       <c r="R101" t="n">
-        <v>6388599</v>
+        <v>6388327</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11663,22 +11538,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11687,38 +11552,33 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195428</t>
+          <t>https://artportalen.se/Sighting/137314141</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137195431</v>
+        <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>87559</v>
+        <v>104949</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11726,37 +11586,33 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>701026</v>
+        <v>700800</v>
       </c>
       <c r="R102" t="n">
-        <v>6388602</v>
+        <v>6388290</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11780,22 +11636,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11810,31 +11656,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195431</t>
+          <t>https://artportalen.se/Sighting/137314144</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137195436</v>
+        <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>87559</v>
+        <v>104949</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11842,37 +11684,33 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>224416</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Väg 143, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700870</v>
+        <v>700815</v>
       </c>
       <c r="R103" t="n">
-        <v>6388557</v>
+        <v>6388283</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11896,22 +11734,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11926,69 +11754,61 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Jan Henriksson, Johan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195436</t>
+          <t>https://artportalen.se/Sighting/137314145</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137195439</v>
+        <v>105104386</v>
       </c>
       <c r="B104" t="n">
-        <v>87559</v>
+        <v>106650</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>225197</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äkta ljungsnärja</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingbomasten 300 m V, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700852</v>
+        <v>701144</v>
       </c>
       <c r="R104" t="n">
-        <v>6388564</v>
+        <v>6388381</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12012,22 +11832,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Rosendal 1:17</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12038,70 +11853,75 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Alvarlik kalkhällmark, parasit på Gulmåra, Ögontröst, Praktbrunört</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna Gotland</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195439</t>
+          <t>https://artportalen.se/Sighting/105104386</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137195446</v>
+        <v>128835480</v>
       </c>
       <c r="B105" t="n">
-        <v>87559</v>
+        <v>92688</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>232138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Follingbo Rosendal, Gtl</t>
+          <t>Follingsbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>701022</v>
+        <v>700814</v>
       </c>
       <c r="R105" t="n">
-        <v>6388627</v>
+        <v>6388491</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12128,22 +11948,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12158,68 +11978,62 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137195446</t>
+          <t>https://artportalen.se/Sighting/128835480</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137199973</v>
+        <v>128833061</v>
       </c>
       <c r="B106" t="n">
-        <v>87559</v>
+        <v>87262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Follingbo,Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>701051</v>
+        <v>700935</v>
       </c>
       <c r="R106" t="n">
-        <v>6388472</v>
+        <v>6388458</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12246,22 +12060,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12270,78 +12074,71 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137199973</t>
+          <t>https://artportalen.se/Sighting/128833061</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137199977</v>
+        <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87559</v>
+        <v>87485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Follingbo,Rosendal, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700856</v>
+        <v>700928</v>
       </c>
       <c r="R107" t="n">
-        <v>6388393</v>
+        <v>6388587</v>
       </c>
       <c r="S107" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12370,7 +12167,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12380,7 +12177,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12389,19 +12186,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bo karlstens, Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12411,38 +12207,38 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137199977</t>
+          <t>https://artportalen.se/Sighting/137195444</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>137241106</v>
+        <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87559</v>
+        <v>87485</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12452,13 +12248,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>701141</v>
+        <v>700919</v>
       </c>
       <c r="R108" t="n">
-        <v>6388510</v>
+        <v>6388559</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12487,7 +12283,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12497,7 +12293,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12528,16 +12324,16 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137241106</t>
+          <t>https://artportalen.se/Sighting/137241119</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>137241111</v>
+        <v>128833052</v>
       </c>
       <c r="B109" t="n">
-        <v>87559</v>
+        <v>87346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12565,17 +12361,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Follingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>701068</v>
+        <v>701151</v>
       </c>
       <c r="R109" t="n">
-        <v>6388581</v>
+        <v>6388524</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12599,22 +12395,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12630,31 +12416,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137241111</t>
+          <t>https://artportalen.se/Sighting/128833052</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>137241112</v>
+        <v>128833053</v>
       </c>
       <c r="B110" t="n">
-        <v>87559</v>
+        <v>87346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12682,17 +12464,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Follingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>701039</v>
+        <v>700979</v>
       </c>
       <c r="R110" t="n">
-        <v>6388600</v>
+        <v>6388550</v>
       </c>
       <c r="S110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12716,22 +12498,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12747,31 +12519,27 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna Gotland</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137241112</t>
+          <t>https://artportalen.se/Sighting/128833053</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>137241126</v>
+        <v>128833054</v>
       </c>
       <c r="B111" t="n">
-        <v>87559</v>
+        <v>87346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12799,17 +12567,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Follingbo, Gtl</t>
+          <t>Follingbo Rosendal, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700812</v>
+        <v>700966</v>
       </c>
       <c r="R111" t="n">
-        <v>6388541</v>
+        <v>6388444</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12833,22 +12601,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12864,20 +12622,2070 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833054</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128833055</v>
+      </c>
+      <c r="B112" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>700996</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6388473</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833055</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128833056</v>
+      </c>
+      <c r="B113" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>701017</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6388485</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833056</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128833057</v>
+      </c>
+      <c r="B114" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>701053</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6388488</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833057</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128835465</v>
+      </c>
+      <c r="B115" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>700869</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6388563</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835465</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128835466</v>
+      </c>
+      <c r="B116" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Follingsbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>700824</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6388554</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128835466</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>137195422</v>
+      </c>
+      <c r="B117" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>701158</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6388516</v>
+      </c>
+      <c r="S117" t="n">
+        <v>6</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195422</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>137195427</v>
+      </c>
+      <c r="B118" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>701052</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6388594</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195427</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>137195428</v>
+      </c>
+      <c r="B119" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>701024</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6388599</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195428</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>137195431</v>
+      </c>
+      <c r="B120" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>701026</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6388602</v>
+      </c>
+      <c r="S120" t="n">
+        <v>6</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195431</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>137195436</v>
+      </c>
+      <c r="B121" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>700870</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6388557</v>
+      </c>
+      <c r="S121" t="n">
+        <v>7</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195436</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>137195439</v>
+      </c>
+      <c r="B122" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>700852</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6388564</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195439</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>137195446</v>
+      </c>
+      <c r="B123" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Follingbo Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>701022</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6388627</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137195446</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>137199973</v>
+      </c>
+      <c r="B124" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Follingbo,Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>701051</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6388472</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137199973</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>137199977</v>
+      </c>
+      <c r="B125" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Follingbo,Rosendal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>700856</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6388393</v>
+      </c>
+      <c r="S125" t="n">
+        <v>19</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137199977</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>137241106</v>
+      </c>
+      <c r="B126" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Follingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>701141</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6388510</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
           <t>Petra Wikström</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr">
+      <c r="AY126" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137241106</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>137241111</v>
+      </c>
+      <c r="B127" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Follingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>701068</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6388581</v>
+      </c>
+      <c r="S127" t="n">
+        <v>7</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137241111</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>137241112</v>
+      </c>
+      <c r="B128" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Follingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>701039</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6388600</v>
+      </c>
+      <c r="S128" t="n">
+        <v>9</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137241112</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>137241126</v>
+      </c>
+      <c r="B129" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Follingbo, Gtl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>700812</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6388541</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Follingbo</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Anna Helmersson, Pia Edfors, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137241126</t>
         </is>
@@ -12995,6 +14803,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93322</v>
+        <v>93323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93322</v>
+        <v>93323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93322</v>
+        <v>93323</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87635</v>
+        <v>87636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87614</v>
+        <v>87615</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89370</v>
+        <v>89371</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111503</v>
+        <v>111504</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104949</v>
+        <v>104950</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93323</v>
+        <v>93328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93323</v>
+        <v>93328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93323</v>
+        <v>93328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87636</v>
+        <v>87639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87615</v>
+        <v>87618</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89371</v>
+        <v>89374</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137241110</v>
       </c>
       <c r="B72" t="n">
-        <v>58895</v>
+        <v>58897</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111504</v>
+        <v>111509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104950</v>
+        <v>104955</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93328</v>
+        <v>93330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93328</v>
+        <v>93330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93328</v>
+        <v>93330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111509</v>
+        <v>111512</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104955</v>
+        <v>104958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93330</v>
+        <v>93336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93330</v>
+        <v>93336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93330</v>
+        <v>93336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87639</v>
+        <v>87644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87618</v>
+        <v>87623</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89374</v>
+        <v>89379</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137241110</v>
       </c>
       <c r="B72" t="n">
-        <v>58897</v>
+        <v>58901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111512</v>
+        <v>111518</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104958</v>
+        <v>104964</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111518</v>
+        <v>111519</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93336</v>
+        <v>93348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93336</v>
+        <v>93348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93336</v>
+        <v>93348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87623</v>
+        <v>87634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89379</v>
+        <v>89390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111519</v>
+        <v>111531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104965</v>
+        <v>104977</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93348</v>
+        <v>93349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87634</v>
+        <v>87635</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111531</v>
+        <v>111532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104977</v>
+        <v>104978</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137195443</v>
       </c>
       <c r="B5" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137199979</v>
       </c>
       <c r="B14" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137241109</v>
       </c>
       <c r="B15" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137195424</v>
       </c>
       <c r="B16" t="n">
-        <v>93349</v>
+        <v>93352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>137195435</v>
       </c>
       <c r="B17" t="n">
-        <v>93349</v>
+        <v>93352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>137195437</v>
       </c>
       <c r="B18" t="n">
-        <v>93349</v>
+        <v>93352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>137241123</v>
       </c>
       <c r="B21" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>137195425</v>
       </c>
       <c r="B34" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>137195426</v>
       </c>
       <c r="B35" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137195432</v>
       </c>
       <c r="B36" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137199975</v>
       </c>
       <c r="B37" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>137241113</v>
       </c>
       <c r="B38" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>137241114</v>
       </c>
       <c r="B39" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>137241115</v>
       </c>
       <c r="B40" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>137241128</v>
       </c>
       <c r="B41" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>137199976</v>
       </c>
       <c r="B45" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>137195429</v>
       </c>
       <c r="B49" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>137195434</v>
       </c>
       <c r="B54" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>137195440</v>
       </c>
       <c r="B55" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>137195442</v>
       </c>
       <c r="B56" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>137195445</v>
       </c>
       <c r="B57" t="n">
-        <v>87635</v>
+        <v>87638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>137241122</v>
       </c>
       <c r="B58" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137199974</v>
       </c>
       <c r="B62" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>137241118</v>
       </c>
       <c r="B63" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>137314147</v>
       </c>
       <c r="B75" t="n">
-        <v>111532</v>
+        <v>111535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>137314136</v>
       </c>
       <c r="B76" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>137314143</v>
       </c>
       <c r="B80" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>137314130</v>
       </c>
       <c r="B82" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>137314134</v>
       </c>
       <c r="B83" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>137314140</v>
       </c>
       <c r="B84" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>137314146</v>
       </c>
       <c r="B85" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>137314198</v>
       </c>
       <c r="B90" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>137314199</v>
       </c>
       <c r="B91" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>137314200</v>
       </c>
       <c r="B92" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>137314201</v>
       </c>
       <c r="B93" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>137314076</v>
       </c>
       <c r="B97" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>137314128</v>
       </c>
       <c r="B98" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137314131</v>
       </c>
       <c r="B99" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>137314139</v>
       </c>
       <c r="B100" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>137314141</v>
       </c>
       <c r="B101" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>137314144</v>
       </c>
       <c r="B102" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>137314145</v>
       </c>
       <c r="B103" t="n">
-        <v>104978</v>
+        <v>104981</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137195444</v>
       </c>
       <c r="B107" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>137241119</v>
       </c>
       <c r="B108" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>137195422</v>
       </c>
       <c r="B117" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>137195427</v>
       </c>
       <c r="B118" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>137195428</v>
       </c>
       <c r="B119" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137195431</v>
       </c>
       <c r="B120" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>137195436</v>
       </c>
       <c r="B121" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>137195439</v>
       </c>
       <c r="B122" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>137195446</v>
       </c>
       <c r="B123" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>137199973</v>
       </c>
       <c r="B124" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>137199977</v>
       </c>
       <c r="B125" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137241106</v>
       </c>
       <c r="B126" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>137241111</v>
       </c>
       <c r="B127" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>137241112</v>
       </c>
       <c r="B128" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>137241126</v>
       </c>
       <c r="B129" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 6153-2024 artfynd.xlsx
+++ b/artfynd/A 6153-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137199971</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>137241107</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137521926</v>
       </c>
       <c r="B5" t="n">
-        <v>87651</v>
+        <v>87654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137195443</v>
       </c>
       <c r="B6" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>137199979</v>
       </c>
       <c r="B15" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>137241109</v>
       </c>
       <c r="B16" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>137195424</v>
       </c>
       <c r="B17" t="n">
-        <v>93352</v>
+        <v>93356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>137195435</v>
       </c>
       <c r="B18" t="n">
-        <v>93352</v>
+        <v>93356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>137195437</v>
       </c>
       <c r="B19" t="n">
-        <v>93352</v>
+        <v>93356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>137241123</v>
       </c>
       <c r="B22" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>137195425</v>
       </c>
       <c r="B35" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>137195426</v>
       </c>
       <c r="B36" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>137195432</v>
       </c>
       <c r="B37" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137199975</v>
       </c>
       <c r="B38" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>137241113</v>
       </c>
       <c r="B39" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>137241114</v>
       </c>
       <c r="B40" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>137241115</v>
       </c>
       <c r="B41" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>137241128</v>
       </c>
       <c r="B42" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>137521925</v>
       </c>
       <c r="B43" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>137521934</v>
       </c>
       <c r="B44" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>137199976</v>
       </c>
       <c r="B48" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>137521929</v>
       </c>
       <c r="B49" t="n">
-        <v>87418</v>
+        <v>87421</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>137521932</v>
       </c>
       <c r="B50" t="n">
-        <v>87418</v>
+        <v>87421</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>137521935</v>
       </c>
       <c r="B51" t="n">
-        <v>87418</v>
+        <v>87421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>137195429</v>
       </c>
       <c r="B55" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>137195434</v>
       </c>
       <c r="B60" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>137195440</v>
       </c>
       <c r="B61" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137195442</v>
       </c>
       <c r="B62" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>137195445</v>
       </c>
       <c r="B63" t="n">
-        <v>87638</v>
+        <v>87642</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>137521939</v>
       </c>
       <c r="B64" t="n">
-        <v>87639</v>
+        <v>87642</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>137241122</v>
       </c>
       <c r="B65" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>137521938</v>
       </c>
       <c r="B69" t="n">
-        <v>91693</v>
+        <v>91696</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>137199974</v>
       </c>
       <c r="B70" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>137241118</v>
       </c>
       <c r="B71" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137241110</v>
       </c>
       <c r="B80" t="n">
-        <v>58901</v>
+        <v>58904</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>137314147</v>
       </c>
       <c r="B83" t="n">
-        <v>111535</v>
+        <v>111541</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>137521940</v>
       </c>
       <c r="B84" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>137314136</v>
       </c>
       <c r="B85" t="n">
-        <v>108211</v>
+        <v>108217</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>137314143</v>
       </c>
       <c r="B89" t="n">
-        <v>110166</v>
+        <v>110172</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>137314130</v>
       </c>
       <c r="B91" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>137314134</v>
       </c>
       <c r="B92" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>137314140</v>
       </c>
       <c r="B93" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>137314146</v>
       </c>
       <c r="B94" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>137314198</v>
       </c>
       <c r="B99" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>137314199</v>
       </c>
       <c r="B100" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>137314200</v>
       </c>
       <c r="B101" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>137314201</v>
       </c>
       <c r="B102" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>137314076</v>
       </c>
       <c r="B106" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>137314128</v>
       </c>
       <c r="B107" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>137314131</v>
       </c>
       <c r="B108" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>137314139</v>
       </c>
       <c r="B109" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>137314141</v>
       </c>
       <c r="B110" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>137314144</v>
       </c>
       <c r="B111" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>137314145</v>
       </c>
       <c r="B112" t="n">
-        <v>104981</v>
+        <v>104987</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>137195444</v>
       </c>
       <c r="B116" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>137241119</v>
       </c>
       <c r="B117" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>137521928</v>
       </c>
       <c r="B118" t="n">
-        <v>87510</v>
+        <v>87513</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>137521930</v>
       </c>
       <c r="B119" t="n">
-        <v>87510</v>
+        <v>87513</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137521936</v>
       </c>
       <c r="B120" t="n">
-        <v>87510</v>
+        <v>87513</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>137195422</v>
       </c>
       <c r="B129" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>137195427</v>
       </c>
       <c r="B130" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>137195428</v>
       </c>
       <c r="B131" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>137195431</v>
       </c>
       <c r="B132" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>137195436</v>
       </c>
       <c r="B133" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>137195439</v>
       </c>
       <c r="B134" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>137195446</v>
       </c>
       <c r="B135" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>137199973</v>
       </c>
       <c r="B136" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>137199977</v>
       </c>
       <c r="B137" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>137241106</v>
       </c>
       <c r="B138" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>137241111</v>
       </c>
       <c r="B139" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>137241112</v>
       </c>
       <c r="B140" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>137241126</v>
       </c>
       <c r="B141" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>137521924</v>
       </c>
       <c r="B142" t="n">
-        <v>87594</v>
+        <v>87597</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>137521931</v>
       </c>
       <c r="B143" t="n">
-        <v>87594</v>
+        <v>87597</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>137521933</v>
       </c>
       <c r="B144" t="n">
-        <v>87594</v>
+        <v>87597</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
